--- a/docs/六镇企业具体地址与经纬度核验表.xlsx
+++ b/docs/六镇企业具体地址与经纬度核验表.xlsx
@@ -1738,7 +1738,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3979,7 +3979,7 @@
       <c r="H20" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" s="19" t="s">
         <v>200</v>
       </c>
       <c r="J20" s="16">
